--- a/data/trans_bre/P1404-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1404-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,59</t>
+          <t>-1,2; 0,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,45</t>
+          <t>-0,78; 0,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,47</t>
+          <t>0,3; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,45</t>
+          <t>0,06; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,4</t>
+          <t>-2,67; 0,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,93</t>
+          <t>-2,25; 0,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,52</t>
+          <t>-0,94; 2,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 714,52</t>
+          <t>-23,35; 691,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,93; 35,07</t>
+          <t>-80,15; 55,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 95,11</t>
+          <t>-69,99; 114,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 532,65</t>
+          <t>-54,58; 584,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-74,47%</t>
+          <t>-64,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,39</t>
+          <t>-2,94; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,55</t>
+          <t>-4,42; 0,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,13</t>
+          <t>-4,07; -0,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -1,78</t>
+          <t>-5,46; -1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 47,13</t>
+          <t>-54,88; 45,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 12,77</t>
+          <t>-59,69; 11,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 3,31</t>
+          <t>-67,2; 0,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,19; -48,1</t>
+          <t>-80,66; -34,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>-27,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,73</t>
+          <t>-5,49; 1,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,79</t>
+          <t>-0,3; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,02</t>
+          <t>-3,25; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 7,42</t>
+          <t>-7,05; -0,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 20,89</t>
+          <t>-45,58; 16,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 91,11</t>
+          <t>-3,88; 98,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 47,55</t>
+          <t>-26,34; 44,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 149,09</t>
+          <t>-43,43; -4,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 9,43</t>
+          <t>-2,36; 8,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,15</t>
+          <t>-0,0; 12,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 9,61</t>
+          <t>-1,82; 9,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,96</t>
+          <t>-2,23; 6,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 62,57</t>
+          <t>-12,54; 55,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 71,85</t>
+          <t>-0,02; 72,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 54,14</t>
+          <t>-7,67; 52,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 23,78</t>
+          <t>-9,03; 29,26</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,81</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 14,83</t>
+          <t>1,5; 14,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 6,1</t>
+          <t>-8,61; 6,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 6,03</t>
+          <t>-8,13; 5,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 52,77</t>
+          <t>0,35; 10,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 88,11</t>
+          <t>5,84; 86,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 19,11</t>
+          <t>-21,48; 21,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 21,23</t>
+          <t>-22,95; 19,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 192,04</t>
+          <t>1,13; 39,06</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 11,63</t>
+          <t>-2,92; 11,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,89</t>
+          <t>-5,49; 10,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,79</t>
+          <t>-5,2; 9,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 11,35</t>
+          <t>-0,3; 10,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 66,04</t>
+          <t>-11,85; 68,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 34,57</t>
+          <t>-14,7; 37,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 36,21</t>
+          <t>-15,21; 37,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 34,73</t>
+          <t>-0,6; 32,74</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>1,03; 3,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,1</t>
+          <t>0,66; 3,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,34</t>
+          <t>0,18; 3,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 23,11</t>
+          <t>0,13; 3,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,48; 51,37</t>
+          <t>12,4; 54,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 39,16</t>
+          <t>4,85; 37,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 31,67</t>
+          <t>1,51; 32,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,24; 180,81</t>
+          <t>0,83; 24,69</t>
         </is>
       </c>
     </row>
